--- a/3_project_presentation/transfer_candidates_table.xlsx
+++ b/3_project_presentation/transfer_candidates_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0c513644393d52d/^NEdu/NCSU 2024-2026/Sem 1/ALDA/engr-ALDA-Fall2024-P28/2_midway/latex/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0c513644393d52d/^NEdu/NCSU 2024-2026/Sem 1/ALDA/engr-ALDA-Fall2024-P28/3_project_presentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{67C89B37-2ECD-4707-9C25-08D3531B97EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13EB3071-E022-4D61-8315-1794320126A3}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{67C89B37-2ECD-4707-9C25-08D3531B97EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A690632B-764C-4087-B2DD-2FC03739EC00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2AC6DD22-4827-4F32-8E64-CC3C42EA44CA}"/>
   </bookViews>
@@ -680,6 +680,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
